--- a/계산모델_엑셀/공정모델링_실험런시트_61런.xlsx
+++ b/계산모델_엑셀/공정모델링_실험런시트_61런.xlsx
@@ -70,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -80,7 +80,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -460,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -476,85 +475,74 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>공정 모델링 실험 런시트 — 설계 설명 [67런 완전판] (1차 실측 반영)</t>
+          <t>공정 모델링 실험 런시트 — 설계 설명 [61런 완전판] (1차 실측 반영)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>대원칙: 정확한 검사결과가 최우선. 시간단축은 정확도 지키는 범위 안에서만. 자재=26µm·86µm(158µm 미보유→86µm 사용).</t>
+          <t>대원칙: 정확한 검사결과 최우선. 자재=26µm·86µm(158µm 미보유→86µm).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 1차 실측 교훈 (★설계 수정 근거 — '1차실측' 시트 참조)</t>
+          <t>■ 1차 실측 교훈 ('1차실측' 시트)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>· 86µm: 양호. kV*≈60.5(Q0.999), R스윕 안정. · 26µm: 미세 R일수록 과소측정·측정실패 (R0.2→Q0.57, R0.5→Q0.82). 원인=광자부족(얇은 범프+작은 픽셀→노이즈에 묻혀 어두운 핵만 잡음). → ①측정 가능 영역에서 kV* 찾기(26µm=R0.5·F32, kV55~58) ②미세 R은 높은 F와 짝(계단식) ③측정실패 조건에 런 배치 금지.</t>
+          <t>86µm 양호(kV*≈60.5). 26µm 미세R서 과소·실패(광자부족) → ①측정 가능 영역서 kV*(26µm=R0.5·F32,kV55~58) ②미세R은 高F 계단식 ③실패조건 금지.</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
-    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ W는 '스크리닝 먼저' (86µm 중간 두께라 W 효과 불확실)</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>■ 정확도 = void 총오차 ≤ 10% = √(픽셀화² + 노이즈²)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>픽셀화(R):2/N≤7%→N≈29 / 노이즈(F,W):2σ≤7%. ★단 26µm은 미세 R이 측정을 깨서 N을 못 키움 → void 정확도가 물리적으로 ~13%(R0.5·N15) 수준에 묶일 수 있음. Phase의 R×F로 'F로 회복 가능한지' 확인.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>■ 정확도 사는 비용 순위: W(시간 공짜) &lt; F(1차) &lt; R(2차). SNR∝√(W·F·t), tact∝F/R².</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>86µm W{4,6}로 void%·σ 반응 확인. 양성일 때만 심화 W블록(R×W·W×F·kV×W), 음성이면 W=4 고정·생략.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>■ 정확도=총오차≤10%=√(픽셀화²+노이즈²). N≈29. 26µm은 미세R 한계로 void정확도 ~13% 가능(R×F 확인).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>미세 R은 광자부족을 부르므로, 정확도는 R을 내리기보다 F(또는 두꺼운 범프면 W)로 사는 게 싸고 안전. 두꺼운/큰 범프: W↑(공짜)로 거친 R 허용. 26µm: R하한+측정한계라 F가 지렛대, 시간은 shot수.</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>■ 정확도 비용: W(공짜)&lt;F(1차)&lt;R(2차). 미세R은 高F로 광자 채움. 교호작용 Phase3.</t>
         </is>
       </c>
     </row>
     <row r="18"/>
-    <row r="19"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>■ 교호작용(Phase3): R×F(26µm)·R×W(86µm)·W×F(86µm) + kV×F·kV×W 가드. 총오차_rel로 비교.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
+    <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A17:H19"/>
-    <mergeCell ref="A15:H16"/>
-    <mergeCell ref="A11:H13"/>
+    <mergeCell ref="A17:H18"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A5:H8"/>
-    <mergeCell ref="A21:H22"/>
+    <mergeCell ref="A5:H7"/>
+    <mergeCell ref="A10:H11"/>
+    <mergeCell ref="A13:H15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,102 +572,102 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>1차 실측 데이터 (설계 수정의 근거)</t>
+          <t>1차 실측 데이터 (설계 수정 근거)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>86µm는 안정(kV*≈60.5). 26µm는 미세 R서 과소측정·실패(광자부족) → 측정 가능 영역/계단식 F로 재설계.</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>86µm 안정(kV*≈60.5). 26µm 미세R서 과소·실패(광자부족).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>PD직경</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>측정직경</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Q_dia</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>kV1</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>26µm</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>55.5</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="G5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>측정실패</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr"/>
-      <c r="J5" s="9" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -826,38 +814,38 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>26µm</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>57.5</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="G10" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="G10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>측정실패</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr"/>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>F32+미세R</t>
         </is>
@@ -1056,106 +1044,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>kV 스윕은 측정되는 (R,F)에서(26µm=R0.5·F32, 86µm=R0.5·F32). R 스윕은 미세R에 高F 짝(계단식). gold=최정밀 측정점.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>kV스윕=측정되는(R,F)에서(26·86µm 모두 R0.5·F32). R스윕=미세R에 高F 계단식. gold=최정밀 측정점.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝(광자부족 회피). D=PD직경/측정직경=종속/void%=측정면적기준.</t>
+          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝. D=PD직경/측정직경=종속/void%=측정면적기준.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="10" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="10" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="10" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr">
+      <c r="R5" s="10" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1788,7 +1776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1821,116 +1809,116 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>같은 범프 반복→σ·총오차. 26µm=F스윕(R0.5, F로 측정회복+σ), 86µm=W스윕(R0.8; W가 86µm서 유효한지). kV*.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>26µm=F스윕(R0.5, 측정회복+σ). 86µm=W 스크리닝{4,6}(효과 유무 판정 — 양성시만 심화 W블록). kV*.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝(광자부족 회피). D=PD직경/측정직경=종속/void%=측정면적기준.</t>
+          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝. D=PD직경/측정직경=종속/void%=측정면적기준.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="10" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="10" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="10" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr">
+      <c r="R5" s="10" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="10" t="inlineStr">
         <is>
           <t>총오차_rel(자동)≤0.10</t>
         </is>
@@ -2398,7 +2386,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2423,7 +2411,7 @@
         <v>32</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -2442,7 +2430,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>W=3 (86µm서 유효?)</t>
+          <t>W=4 스크리닝(W 효과 유무)</t>
         </is>
       </c>
       <c r="S15">
@@ -2457,7 +2445,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2482,7 +2470,7 @@
         <v>32</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
@@ -2504,7 +2492,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2529,7 +2517,7 @@
         <v>32</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
         <v>3</v>
@@ -2551,7 +2539,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2576,7 +2564,7 @@
         <v>32</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -2595,7 +2583,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>W=4 (86µm서 유효?)</t>
+          <t>W=6 스크리닝(W 효과 유무)</t>
         </is>
       </c>
       <c r="S18">
@@ -2610,7 +2598,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2635,7 +2623,7 @@
         <v>32</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
@@ -2657,7 +2645,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2682,7 +2670,7 @@
         <v>32</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
         <v>3</v>
@@ -2700,312 +2688,6 @@
         <v/>
       </c>
       <c r="R20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>86µm</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>86</v>
-      </c>
-      <c r="D21" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F21">
-        <f>IFERROR(ROUND(C21*0.2828/E21,0),"")</f>
-        <v/>
-      </c>
-      <c r="G21" t="n">
-        <v>32</v>
-      </c>
-      <c r="H21" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <f>IFERROR(J21/C21,"")</f>
-        <v/>
-      </c>
-      <c r="O21">
-        <f>IFERROR((M21-N21)/N21,"")</f>
-        <v/>
-      </c>
-      <c r="P21">
-        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(O21)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>W=5 (86µm서 유효?)</t>
-        </is>
-      </c>
-      <c r="S21">
-        <f>IFERROR(STDEV(M21:M23)/AVERAGE(M21:M23),"")</f>
-        <v/>
-      </c>
-      <c r="T21">
-        <f>IFERROR(SQRT(((AVERAGE(M21:M23)-N21)/N21)^2+(2*STDEV(M21:M23)/AVERAGE(M21:M23))^2),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>86µm</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>86</v>
-      </c>
-      <c r="D22" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F22">
-        <f>IFERROR(ROUND(C22*0.2828/E22,0),"")</f>
-        <v/>
-      </c>
-      <c r="G22" t="n">
-        <v>32</v>
-      </c>
-      <c r="H22" t="n">
-        <v>5</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22">
-        <f>IFERROR(J22/C22,"")</f>
-        <v/>
-      </c>
-      <c r="O22">
-        <f>IFERROR((M22-N22)/N22,"")</f>
-        <v/>
-      </c>
-      <c r="P22">
-        <f>IF(J22="","",IF(AND(L22="Y",K22&gt;=0.97,K22&lt;=1.03,IFERROR(ABS(O22)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>86µm</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>86</v>
-      </c>
-      <c r="D23" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F23">
-        <f>IFERROR(ROUND(C23*0.2828/E23,0),"")</f>
-        <v/>
-      </c>
-      <c r="G23" t="n">
-        <v>32</v>
-      </c>
-      <c r="H23" t="n">
-        <v>5</v>
-      </c>
-      <c r="I23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23">
-        <f>IFERROR(J23/C23,"")</f>
-        <v/>
-      </c>
-      <c r="O23">
-        <f>IFERROR((M23-N23)/N23,"")</f>
-        <v/>
-      </c>
-      <c r="P23">
-        <f>IF(J23="","",IF(AND(L23="Y",K23&gt;=0.97,K23&lt;=1.03,IFERROR(ABS(O23)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>86µm</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>86</v>
-      </c>
-      <c r="D24" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F24">
-        <f>IFERROR(ROUND(C24*0.2828/E24,0),"")</f>
-        <v/>
-      </c>
-      <c r="G24" t="n">
-        <v>32</v>
-      </c>
-      <c r="H24" t="n">
-        <v>6</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24">
-        <f>IFERROR(J24/C24,"")</f>
-        <v/>
-      </c>
-      <c r="O24">
-        <f>IFERROR((M24-N24)/N24,"")</f>
-        <v/>
-      </c>
-      <c r="P24">
-        <f>IF(J24="","",IF(AND(L24="Y",K24&gt;=0.97,K24&lt;=1.03,IFERROR(ABS(O24)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>W=6 (86µm서 유효?)</t>
-        </is>
-      </c>
-      <c r="S24">
-        <f>IFERROR(STDEV(M24:M26)/AVERAGE(M24:M26),"")</f>
-        <v/>
-      </c>
-      <c r="T24">
-        <f>IFERROR(SQRT(((AVERAGE(M24:M26)-N24)/N24)^2+(2*STDEV(M24:M26)/AVERAGE(M24:M26))^2),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>86µm</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>86</v>
-      </c>
-      <c r="D25" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F25">
-        <f>IFERROR(ROUND(C25*0.2828/E25,0),"")</f>
-        <v/>
-      </c>
-      <c r="G25" t="n">
-        <v>32</v>
-      </c>
-      <c r="H25" t="n">
-        <v>6</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25">
-        <f>IFERROR(J25/C25,"")</f>
-        <v/>
-      </c>
-      <c r="O25">
-        <f>IFERROR((M25-N25)/N25,"")</f>
-        <v/>
-      </c>
-      <c r="P25">
-        <f>IF(J25="","",IF(AND(L25="Y",K25&gt;=0.97,K25&lt;=1.03,IFERROR(ABS(O25)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>86µm</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>86</v>
-      </c>
-      <c r="D26" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F26">
-        <f>IFERROR(ROUND(C26*0.2828/E26,0),"")</f>
-        <v/>
-      </c>
-      <c r="G26" t="n">
-        <v>32</v>
-      </c>
-      <c r="H26" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26">
-        <f>IFERROR(J26/C26,"")</f>
-        <v/>
-      </c>
-      <c r="O26">
-        <f>IFERROR((M26-N26)/N26,"")</f>
-        <v/>
-      </c>
-      <c r="P26">
-        <f>IF(J26="","",IF(AND(L26="Y",K26&gt;=0.97,K26&lt;=1.03,IFERROR(ABS(O26)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3055,116 +2737,116 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>R×F(26µm 광자부족 회복)·R×W(86µm)·W×F(86µm) + kV×F·kV×W 가드.</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>R×F(26µm 필수) + [조건부:W스크리닝 양성시] R×W·W×F·kV×W(86µm) + kV×F 가드.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝(광자부족 회피). D=PD직경/측정직경=종속/void%=측정면적기준.</t>
+          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝. D=PD직경/측정직경=종속/void%=측정면적기준.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="10" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="10" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="10" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr">
+      <c r="R5" s="10" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="10" t="inlineStr">
         <is>
           <t>총오차_rel(자동)≤0.10</t>
         </is>
@@ -3597,22 +3279,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>gKF</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>86µm</t>
+          <t>26µm</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>60.5</v>
+        <v>58</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -3641,50 +3323,42 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>R0.8×W4(N30)</t>
-        </is>
-      </c>
-      <c r="S14">
-        <f>IFERROR(STDEV(M14:M15)/AVERAGE(M14:M15),"")</f>
-        <v/>
-      </c>
-      <c r="T14">
-        <f>IFERROR(SQRT(((AVERAGE(M14:M15)-N14)/N14)^2+(2*STDEV(M14:M15)/AVERAGE(M14:M15))^2),"")</f>
-        <v/>
+          <t>kV×F가드: 가장자리kV·F32</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>gKF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>86µm</t>
+          <t>26µm</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>60.5</v>
+        <v>58</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
         <v/>
       </c>
       <c r="G15" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="H15" t="n">
         <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <f>IFERROR(J15/C15,"")</f>
@@ -3698,7 +3372,11 @@
         <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>kV×F가드: 가장자리kV·F128 (구제?)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3728,7 +3406,7 @@
         <v>32</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -3747,7 +3425,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>R0.8×W6(N30)</t>
+          <t>[W양성시] R0.8×W4(N30)</t>
         </is>
       </c>
       <c r="S16">
@@ -3787,7 +3465,7 @@
         <v>32</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
@@ -3824,7 +3502,7 @@
         <v>60.5</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F18">
         <f>IFERROR(ROUND(C18*0.2828/E18,0),"")</f>
@@ -3834,7 +3512,7 @@
         <v>32</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -3853,7 +3531,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>R1.5×W4(N16)</t>
+          <t>[W양성시] R0.8×W6(N30)</t>
         </is>
       </c>
       <c r="S18">
@@ -3883,7 +3561,7 @@
         <v>60.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F19">
         <f>IFERROR(ROUND(C19*0.2828/E19,0),"")</f>
@@ -3893,7 +3571,7 @@
         <v>32</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
@@ -3940,7 +3618,7 @@
         <v>32</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -3959,7 +3637,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>R1.5×W6(N16) [거친R+高W=빠름]</t>
+          <t>[W양성시] R1.5×W4(N16)</t>
         </is>
       </c>
       <c r="S20">
@@ -3999,7 +3677,7 @@
         <v>32</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
@@ -4021,7 +3699,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4036,7 +3714,7 @@
         <v>60.5</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="F22">
         <f>IFERROR(ROUND(C22*0.2828/E22,0),"")</f>
@@ -4046,7 +3724,7 @@
         <v>32</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -4065,7 +3743,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>W4×F32</t>
+          <t>[W양성시] R1.5×W6(N16) [거친R+高W=빠름]</t>
         </is>
       </c>
       <c r="S22">
@@ -4080,7 +3758,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WF</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4095,7 +3773,7 @@
         <v>60.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="F23">
         <f>IFERROR(ROUND(C23*0.2828/E23,0),"")</f>
@@ -4105,7 +3783,7 @@
         <v>32</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
@@ -4149,7 +3827,7 @@
         <v/>
       </c>
       <c r="G24" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H24" t="n">
         <v>4</v>
@@ -4171,7 +3849,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>W4×F64</t>
+          <t>[W양성시] W4×F32</t>
         </is>
       </c>
       <c r="S24">
@@ -4208,7 +3886,7 @@
         <v/>
       </c>
       <c r="G25" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H25" t="n">
         <v>4</v>
@@ -4255,10 +3933,10 @@
         <v/>
       </c>
       <c r="G26" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -4277,7 +3955,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>W6×F32</t>
+          <t>[W양성시] W4×F64</t>
         </is>
       </c>
       <c r="S26">
@@ -4314,10 +3992,10 @@
         <v/>
       </c>
       <c r="G27" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
@@ -4361,7 +4039,7 @@
         <v/>
       </c>
       <c r="G28" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H28" t="n">
         <v>6</v>
@@ -4383,7 +4061,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>W6×F64</t>
+          <t>[W양성시] W6×F32</t>
         </is>
       </c>
       <c r="S28">
@@ -4420,7 +4098,7 @@
         <v/>
       </c>
       <c r="G29" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H29" t="n">
         <v>6</v>
@@ -4445,32 +4123,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gKF</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>26µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>60.5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F30">
         <f>IFERROR(ROUND(C30*0.2828/E30,0),"")</f>
         <v/>
       </c>
       <c r="G30" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -4489,42 +4167,50 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>kV×F가드: 가장자리kV·F32</t>
-        </is>
+          <t>[W양성시] W6×F64</t>
+        </is>
+      </c>
+      <c r="S30">
+        <f>IFERROR(STDEV(M30:M31)/AVERAGE(M30:M31),"")</f>
+        <v/>
+      </c>
+      <c r="T30">
+        <f>IFERROR(SQRT(((AVERAGE(M30:M31)-N30)/N30)^2+(2*STDEV(M30:M31)/AVERAGE(M30:M31))^2),"")</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gKF</t>
+          <t>WF</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>26µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="D31" t="n">
-        <v>58</v>
+        <v>60.5</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F31">
         <f>IFERROR(ROUND(C31*0.2828/E31,0),"")</f>
         <v/>
       </c>
       <c r="G31" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31">
         <f>IFERROR(J31/C31,"")</f>
@@ -4538,11 +4224,7 @@
         <f>IF(J31="","",IF(AND(L31="Y",K31&gt;=0.97,K31&lt;=1.03,IFERROR(ABS(O31)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>kV×F가드: 가장자리kV·F128 (구제?)</t>
-        </is>
-      </c>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4591,7 +4273,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>kV×W가드: 저kV·W4</t>
+          <t>[W양성시] kV×W가드: 저kV·W4</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4324,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>kV×W가드: 저kV·W6 (W 소용?)</t>
+          <t>[W양성시] kV×W가드: 저kV·W6</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4376,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>모델 산출로 자재별 ×3반복. 합격: 매칭Y &amp; Q_dia97~103% &amp; 총오차_rel≤10% &amp; tact 최소.</t>
         </is>
@@ -4703,107 +4385,107 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝(광자부족 회피). D=PD직경/측정직경=종속/void%=측정면적기준.</t>
+          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝. D=PD직경/측정직경=종속/void%=측정면적기준.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="10" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="10" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="10" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr">
+      <c r="R5" s="10" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="10" t="inlineStr">
         <is>
           <t>총오차_rel(자동)≤0.10</t>
         </is>
@@ -4864,7 +4546,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>26µm 정확도 한계 확인(R×F 결과 반영)</t>
+          <t>26µm 정확도 한계 확인</t>
         </is>
       </c>
       <c r="S6">
@@ -5041,7 +4723,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>정확도 확인 (W로 R 거칠게 최적)</t>
+          <t>정확도 확인</t>
         </is>
       </c>
       <c r="S9">
@@ -5178,7 +4860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5194,14 +4876,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>역설계 모델 — 측정 가능+정확도(총오차≤10%) 만족 설정 중 최소 tact</t>
+          <t>역설계 모델 — 측정 가능+정확도(총오차≤10%) 만족 중 최소 tact</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ 실측 반영 요점</t>
+          <t>■ 실측·W 반영</t>
         </is>
       </c>
     </row>
@@ -5213,7 +4895,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>≈56 (R0.5·F32서 스윕). 미세R서는 측정 자체가 깨져 kV* 못찾음</t>
+          <t>≈56 (R0.5·F32). 미세R서 측정 깨짐</t>
         </is>
       </c>
     </row>
@@ -5225,7 +4907,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>≈60.5 (Q0.999). 안정</t>
+          <t>≈60.5</t>
         </is>
       </c>
     </row>
@@ -5237,95 +4919,49 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>미세 R엔 高F 필수(광자부족→과소측정·실패). R×F로 회복폭 확정</t>
+          <t>미세R엔 高F 필수. R×F로 회복폭</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>W 스크리닝</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>86µm W{4,6} 효과 유무 먼저. 음성이면 W=4·심화 생략</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
           <t>26µm 한계</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>미세R 회복 안되면 R0.5(N15)·void정확도~13%가 물리 한계 — 수용 여부 결정 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>■ 역설계 규칙</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>미세R 회복 안되면 R0.5(N15)·정확도~13%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>1) kV</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>측정되는 (R,F)에서 kV*(D) 트림→측정직경=PD(100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>2) 정확도 순서</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>경계 흐리면: 86µm=W↑(공짜)→F↑ / 26µm=F↑ (R하한·측정한계)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>3) R</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>정확도 남으면 R↑(2차, 비쌈)로 shot↓. 미세R 필요시 高F 동반</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4) 검증</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>측정성공 &amp; 총오차≤10% &amp; 매칭 &amp; Q_dia 후 tact</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>※ 확정 계수는 레시피모델·계산기에 반영. 26µm 정확도 한계는 데이터로 확정 후 tolerance 재검토.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>■ 규칙: kV*트림→(W양성시 W↑공짜)→F↑→R↑ 순 정확도, 그 안 tact 최소.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="A15:H16"/>
+  <mergeCells count="6">
+    <mergeCell ref="B8:H8"/>
     <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B12:H12"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="A10:H11"/>
     <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B11:H11"/>
     <mergeCell ref="B5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
